--- a/prompt.xlsx
+++ b/prompt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Thesis\Text2Cypher Cable Harness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{724C230A-6FCE-4DE8-BCD4-C91105519CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D498DD4-50A9-49CD-B8F4-A5D5BCD350D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,11 +57,6 @@
     <t>On what date was the first cable set produced?</t>
   </si>
   <si>
-    <t>Categorization: Components are not labeled `:Connector`. Instead, they are generic `:Component` nodes linked to a `:Type` node.
-Connector Identification: A component is a connector if it has a `[:hasType]` relationship to a `:Type` node where the `code` is 'connector'.
-Logic: Match the pattern `(Component)-[:hasType]-&gt;(Type)` and filter the Type node.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Component Occurrence: An actual usage of a component is represented by a node labeled `:Component:Occurrence`.
 Relationship: These occurrence nodes point TO the main definition node via the `[:is]` relationship: `(Definition)&lt;-[:is]-(Occurrence)`.
 Logic: To find the most used component, count how many incoming `[:is]` relationships each `:Component` definition has from `:Component:Occurrence` nodes.
@@ -155,6 +150,11 @@
   </si>
   <si>
     <t>What processes are carried out to manufacture a cable set for SL641018 ?</t>
+  </si>
+  <si>
+    <t>Categorization: Components are not labeled 'Connector'. Instead, they are generic 'Component' nodes linked to a 'Type' node.
+Connector Identification: A component is a connector if it has a `[:hasType]` relationship to a `:Type` node where the `code` is 'connector'.
+Logic: Match the pattern `(Component)-[:hasType]-&gt;(Type)` and filter the Type node.</t>
   </si>
 </sst>
 </file>
@@ -497,10 +497,10 @@
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -508,10 +508,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -519,10 +519,10 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -530,10 +530,10 @@
         <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -541,21 +541,21 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -563,10 +563,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="104" customHeight="1" x14ac:dyDescent="0.35">
@@ -574,10 +574,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
